--- a/Donnees/Statistiques Démographiques et sociales/Education/Theme_Education (3).xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Education/Theme_Education (3).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Démographiques et sociales\Education\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214C44C1-2322-4F6B-AD7D-3644EC6636A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAA4323-87E3-4811-97AA-A40A3E361472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="54">
-  <si>
-    <t>Tableau 1.2.4: Evolution du Taux Net de Scolarisation (TNS) au Fondamental pour les Garçons par Wilaya durant la période 2006-2023</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="55">
   <si>
     <t>2006/2007</t>
   </si>
@@ -99,15 +96,6 @@
     <t>Source : MENRSE, Annuaires des Statistiques Scolaires</t>
   </si>
   <si>
-    <t>Tableau 1.2.5: Evolution du Taux Net de Scolarisation (TNS) au Fondamental pour les filles par Wilaya, durant la période 2006-2023</t>
-  </si>
-  <si>
-    <t>Tableau 1.2.6: Evolution du Taux Net de Scolarisation (TNS) au Fondamental pour les deux sexes par Wilaya, durant la période 2006-2023</t>
-  </si>
-  <si>
-    <t>Tableau 1.2.1 : Evolution du taux d’analphabétisme selon la wilaya et le sexe durant la période 2000-2023</t>
-  </si>
-  <si>
     <t>2000~Féminin</t>
   </si>
   <si>
@@ -138,9 +126,6 @@
     <t>Source : RGPH/2000-2023</t>
   </si>
   <si>
-    <t>Tableau 1.2.3: Evolution du taux brut de scolarisation dans le fondamentale (en %) par milieu de résdence selon le sexe durant la période 2000-2023</t>
-  </si>
-  <si>
     <t>Sexe~Féminin</t>
   </si>
   <si>
@@ -174,9 +159,6 @@
     <t>2023~Rural</t>
   </si>
   <si>
-    <t>Tableau 1.2.2: Taux brut de scolarisation pour le fondamentale selon la wilaya et par sexe, 2000-2023</t>
-  </si>
-  <si>
     <t>Sexe~Total</t>
   </si>
   <si>
@@ -187,6 +169,27 @@
   </si>
   <si>
     <t>88.1</t>
+  </si>
+  <si>
+    <t>Tableau 1.2.1 : Evolution du taux d’analphabétisme selon la wilaya et le sexe 2000-2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* A partir de 2014 Nouakchott a été subdivisée en trois wilayas </t>
+  </si>
+  <si>
+    <t>Tableau 1.2.2: Taux brut de scolarisation au fondamental par wilaya et selon le sexe, 2000-2023</t>
+  </si>
+  <si>
+    <t>Tableau 1.2.3: Evolution du taux brut de scolarisation au fondamental (en %) par milieu de résidence et selon le sexe 2000-2023</t>
+  </si>
+  <si>
+    <t>Tableau 1.2.4: Evolution du Taux Net de Scolarisation (TNS) au fondamental pour les garçons par wilaya 2006-2023</t>
+  </si>
+  <si>
+    <t>Tableau 1.2.5: Evolution du Taux Net de Scolarisation (TNS) au fondamental pour les filles par wilaya, 2006-2023</t>
+  </si>
+  <si>
+    <t>Tableau 1.2.6: Evolution du Taux Net de Scolarisation (TNS) au fondamental par wilaya, 2006-2023</t>
   </si>
 </sst>
 </file>
@@ -547,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="110.44140625" bestFit="1" customWidth="1"/>
@@ -555,42 +558,42 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>39.200000000000003</v>
@@ -622,7 +625,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>51.8</v>
@@ -654,7 +657,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>57.8</v>
@@ -686,7 +689,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>50.3</v>
@@ -718,7 +721,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>63.7</v>
@@ -750,7 +753,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>44.5</v>
@@ -782,7 +785,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>28.3</v>
@@ -814,7 +817,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>32.200000000000003</v>
@@ -846,7 +849,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>19.7</v>
@@ -878,7 +881,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>45.7</v>
@@ -910,7 +913,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>58.7</v>
@@ -942,7 +945,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>22.1</v>
@@ -974,7 +977,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>30</v>
@@ -1006,7 +1009,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>18.600000000000001</v>
@@ -1038,7 +1041,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H17">
         <v>14.4</v>
@@ -1052,7 +1055,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H18">
         <v>13.8</v>
@@ -1066,7 +1069,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H19">
         <v>16.5</v>
@@ -1080,7 +1083,12 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1098,42 +1106,42 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>68</v>
@@ -1165,7 +1173,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>56.2</v>
@@ -1197,7 +1205,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>45.1</v>
@@ -1229,7 +1237,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>50.1</v>
@@ -1261,7 +1269,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>51.8</v>
@@ -1293,7 +1301,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>64.8</v>
@@ -1325,7 +1333,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>70.7</v>
@@ -1357,7 +1365,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>98.1</v>
@@ -1389,7 +1397,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>107.8</v>
@@ -1421,7 +1429,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>77.2</v>
@@ -1453,7 +1461,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>45.2</v>
@@ -1485,7 +1493,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>111.1</v>
@@ -1517,7 +1525,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>79.599999999999994</v>
@@ -1549,7 +1557,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>101.7</v>
@@ -1581,7 +1589,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H17">
         <v>100</v>
@@ -1595,7 +1603,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H18">
         <v>106.3</v>
@@ -1609,7 +1617,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H19">
         <v>106.3</v>
@@ -1623,7 +1631,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1643,24 +1651,24 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>68</v>
@@ -1674,7 +1682,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>98.5</v>
@@ -1688,7 +1696,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>56.3</v>
@@ -1702,7 +1710,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>70.5</v>
@@ -1716,7 +1724,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>90.7</v>
@@ -1730,7 +1738,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>56.2</v>
@@ -1744,7 +1752,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>92</v>
@@ -1758,7 +1766,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>106</v>
@@ -1772,7 +1780,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>79.400000000000006</v>
@@ -1786,7 +1794,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1805,39 +1813,39 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>74.599999999999994</v>
@@ -1866,7 +1874,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>64.8</v>
@@ -1895,7 +1903,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>85.3</v>
@@ -1924,7 +1932,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>73.8</v>
@@ -1953,7 +1961,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>68.3</v>
@@ -1982,7 +1990,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>72.2</v>
@@ -1994,7 +2002,7 @@
         <v>74.7</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F8">
         <v>90.6</v>
@@ -2011,7 +2019,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>80.8</v>
@@ -2040,7 +2048,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>77</v>
@@ -2069,7 +2077,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>73.3</v>
@@ -2098,7 +2106,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>100.1</v>
@@ -2127,7 +2135,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>73.8</v>
@@ -2139,7 +2147,7 @@
         <v>85.7</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F13">
         <v>88.99</v>
@@ -2156,7 +2164,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>75.7</v>
@@ -2185,7 +2193,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>72.8</v>
@@ -2214,7 +2222,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>74.2</v>
@@ -2243,7 +2251,7 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2258,39 +2266,39 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>78.8</v>
@@ -2319,7 +2327,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>68.3</v>
@@ -2348,7 +2356,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>99.9</v>
@@ -2377,7 +2385,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>76.400000000000006</v>
@@ -2406,7 +2414,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>69.7</v>
@@ -2435,7 +2443,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>75.7</v>
@@ -2464,7 +2472,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>82.8</v>
@@ -2493,7 +2501,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>75.099999999999994</v>
@@ -2522,7 +2530,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>77.099999999999994</v>
@@ -2551,7 +2559,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>102.7</v>
@@ -2580,7 +2588,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>74.2</v>
@@ -2609,7 +2617,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>71.400000000000006</v>
@@ -2638,7 +2646,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>68.599999999999994</v>
@@ -2667,7 +2675,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>80.900000000000006</v>
@@ -2696,7 +2704,7 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2714,39 +2722,39 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>76.7</v>
@@ -2775,7 +2783,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>66.5</v>
@@ -2804,7 +2812,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>92.5</v>
@@ -2833,7 +2841,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>75.099999999999994</v>
@@ -2862,7 +2870,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>69</v>
@@ -2888,7 +2896,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>73.900000000000006</v>
@@ -2917,7 +2925,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>81.8</v>
@@ -2946,7 +2954,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>76.099999999999994</v>
@@ -2975,7 +2983,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>75.099999999999994</v>
@@ -3004,7 +3012,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>101.4</v>
@@ -3016,7 +3024,7 @@
         <v>82.2</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F12">
         <v>85.4</v>
@@ -3033,7 +3041,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>74</v>
@@ -3062,7 +3070,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>73.599999999999994</v>
@@ -3091,7 +3099,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>70.7</v>
@@ -3120,7 +3128,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>77.400000000000006</v>
@@ -3149,7 +3157,7 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
